--- a/agile_methodologyFiles/Unit_Test_Plan_v0.1.xlsx
+++ b/agile_methodologyFiles/Unit_Test_Plan_v0.1.xlsx
@@ -512,12 +512,12 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>UT_01_Chat_Empty_Input</t>
+          <t>UT_01_Eval_Input_Validation</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>Send POST request to /api/chat with empty question payload</t>
+          <t>Send POST request to /api/evaluate with empty question or whitespace payload</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr">
@@ -542,22 +542,22 @@
       </c>
       <c r="B3" s="1" t="inlineStr">
         <is>
-          <t>UT_02_Chat_Gemini_Generation</t>
+          <t>UT_02_Eval_Missing_AI_Response</t>
         </is>
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>Send POST request to /api/chat with valid user question</t>
+          <t>Send POST request to /api/evaluate with valid question but blank ai_response</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr">
         <is>
-          <t>Question string is valid and non-empty</t>
+          <t>ai_response parameter is empty</t>
         </is>
       </c>
       <c r="E3" s="1" t="inlineStr">
         <is>
-          <t>HTTP 200 returned with valid generated text response</t>
+          <t>HTTP 400 Bad Request returned with 'AI response cannot be empty'</t>
         </is>
       </c>
       <c r="F3" s="1" t="inlineStr">
@@ -572,22 +572,22 @@
       </c>
       <c r="B4" s="1" t="inlineStr">
         <is>
-          <t>UT_03_FAISS_Index_Load</t>
+          <t>UT_03_PDF_Extraction_Upload</t>
         </is>
       </c>
       <c r="C4" s="1" t="inlineStr">
         <is>
-          <t>Call retrieve() function without explicitly initializing index in memory</t>
+          <t>Upload a valid PDF document with evaluation input to /api/evaluate</t>
         </is>
       </c>
       <c r="D4" s="1" t="inlineStr">
         <is>
-          <t>Index lazy loads from faiss.index and metadata.json on disk</t>
+          <t>PyMuPDF document text extraction and in-memory chunking</t>
         </is>
       </c>
       <c r="E4" s="1" t="inlineStr">
         <is>
-          <t>FAISS IndexFlatIP loaded successfully with 2,766 chunk vectors</t>
+          <t>HTTP 200 returned with document text extracted and indexed alongside query</t>
         </is>
       </c>
       <c r="F4" s="1" t="inlineStr">
@@ -602,27 +602,27 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>UT_04_Semantic_Retrieval_Ranking</t>
+          <t>UT_04_FAISS_Index_Load</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>Query retrieval module with 'What happens if you smash a mirror?' and top_k=5</t>
+          <t>Call retrieve() function without initializing index in memory beforehand</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr">
         <is>
-          <t>Exact semantic match against TruthfulQA benchmark corpus</t>
+          <t>Index lazy loads from faiss.index and metadata.json on disk</t>
         </is>
       </c>
       <c r="E5" s="1" t="inlineStr">
         <is>
-          <t>Top retrieved chunk is TruthfulQA mirror question with cosine similarity &gt; 0.85</t>
+          <t>FAISS IndexFlatIP loaded successfully with 2,766 chunk vectors</t>
         </is>
       </c>
       <c r="F5" s="1" t="inlineStr">
         <is>
-          <t>Passed (0.9200 similarity)</t>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -632,27 +632,27 @@
       </c>
       <c r="B6" s="1" t="inlineStr">
         <is>
-          <t>UT_05_Retrieval_OutOfDomain</t>
+          <t>UT_05_TruthfulQA_Semantic_Retrieval</t>
         </is>
       </c>
       <c r="C6" s="1" t="inlineStr">
         <is>
-          <t>Query retrieval module with question not present in TruthfulQA or SQuAD contexts</t>
+          <t>Query retrieval module with TruthfulQA mirror benchmark query and top_k=5</t>
         </is>
       </c>
       <c r="D6" s="1" t="inlineStr">
         <is>
-          <t>Semantic similarity search on out-of-domain query</t>
+          <t>Exact semantic match against TruthfulQA benchmark corpus</t>
         </is>
       </c>
       <c r="E6" s="1" t="inlineStr">
         <is>
-          <t>Returns top 5 nearest chunks with low similarity scores (&lt; 0.50) without errors</t>
+          <t>Top retrieved chunk is TruthfulQA mirror question with cosine similarity &gt;= 0.85</t>
         </is>
       </c>
       <c r="F6" s="1" t="inlineStr">
         <is>
-          <t>Passed (scores ~0.31-0.32)</t>
+          <t>Passed (0.9200 similarity)</t>
         </is>
       </c>
     </row>
@@ -662,27 +662,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>UT_06_Evaluate_Endpoint_Valid</t>
+          <t>UT_06_OutOfDomain_Retrieval</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Send POST request to /api/evaluate with question, ai_response, and reference_answer</t>
+          <t>Query retrieval module with query outside benchmark knowledge base</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Valid evaluation payload containing question and response text</t>
+          <t>Cosine similarity search on out-of-domain query</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>HTTP 200 returned with input echo, 5 retrieved evidence chunks, and empty score placeholders</t>
+          <t>Returns nearest chunks with low similarity scores (&lt; 0.50) without errors</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>Passed (scores ~0.31-0.33)</t>
         </is>
       </c>
     </row>
@@ -692,22 +692,22 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>UT_07_Evaluate_Missing_Response</t>
+          <t>UT_07_Database_Record_Persistence</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Send POST request to /api/evaluate with empty ai_response</t>
+          <t>Complete an evaluation run and query GET /api/history</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>ai_response parameter is blank</t>
+          <t>PostgreSQL table insertion and history query</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>HTTP 400 Bad Request returned with 'AI response cannot be empty'</t>
+          <t>HTTP 200 returned with evaluation record present in records list</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">

--- a/agile_methodologyFiles/Unit_Test_Plan_v0.1.xlsx
+++ b/agile_methodologyFiles/Unit_Test_Plan_v0.1.xlsx
@@ -464,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="12.75"/>
   <cols>
     <col width="9.140625" customWidth="1" min="1" max="1"/>
@@ -716,6 +716,216 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>UT_08_Relevance_Scoring_Rubric</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Submit fully relevant vs off-topic responses to evaluate_relevance()</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Bounded 1.0 - 5.0 score and category assignment</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Score &gt;= 4.5 for relevant and &lt;= 2.0 for off-topic with alignment points</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>UT_09_Closed_World_Zero_Evidence</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Submit out-of-domain query with no reference answer and empty KB chunks to evaluate_accuracy()</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Closed-world unverified edge case handling</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Returns score 3.0, Insufficient Evidence category, and is_insufficient_evidence=True</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>UT_10_Contradiction_Detection</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Submit response where reference answer directly conflicts with retrieved benchmark evidence</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Contradiction detection between reference and KB chunks</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Sets contradiction_detected=True and assigns Contradictory category</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>UT_11_Hallucination_Statement_Flagging</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Submit response containing debunked 10% brain myth to evaluate_hallucination()</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Fine-grained statement classification and ungrounded claim flagging</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Flags specific myth claim as Fabricated/Unsupported with cited violation explanation</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>UT_12_Gemini_Multi_Model_Fallback</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Invoke generate_with_fallback() with simulated model deprecation or rate limit</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Model failover to secondary candidate models</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Automatically falls back to gemini-3.7-flash/3.1-flash-lite without raising exception</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>UT_13_Consensus_Verdict_Unverified</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Synthesize final verdict when is_insufficient_evidence is True</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Verdict agent UNVERIFIED status synthesis</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Returns UNVERIFIED verdict with closed-world explanation</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>UT_14_Tabbed_Overview_Grid_Layout</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Render evaluation results in frontend and switch to All 4 Overview tab</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Equal height 2x2 grid alignment across all 4 judge cards</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>All 4 cards render with identical dimensions and consistent rectangular alignment</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>

--- a/agile_methodologyFiles/Unit_Test_Plan_v0.1.xlsx
+++ b/agile_methodologyFiles/Unit_Test_Plan_v0.1.xlsx
@@ -464,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="12.75"/>
   <cols>
     <col width="9.140625" customWidth="1" min="1" max="1"/>
@@ -926,6 +926,246 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>UT_15_Completeness_Omission_Detection</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Submit 3-part question with AI response only answering 1 part to evaluate_completeness()</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Query contains multiple sub-questions with partial answer coverage</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Score &lt;= 2.5, missing_aspects contains the 2 omitted parts with clear omission rationale</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>UT_16_Verdict_Weighted_Composite_Scoring</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Supply deterministic mock scores (Rel: 5, Acc: 4, Hal: 4, Comp: 4) to generate_verdict()</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Weighted formula: 0.35*4 + 0.30*4 + 0.20*5 + 0.15*4 = 4.20</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Returns composite_score == 4.20 and final_verdict == 'Pass'</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Passed (composite_score: 4.20, Pass)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>UT_17_CSV_Batch_Validation_And_Parsing</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Upload CSV with valid headers, optional reference column, and 10 QA pairs to POST /api/batch/upload</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>CSV file validation, header mapping, and row structure parsing</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>HTTP 200 returned with valid row count, parsed preview, and batch_id</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>UT_18_Batch_Execution_Row_Fault_Tolerance</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Execute batch run where row 3 has malformed payload or transient network timeout</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Isolated row failure during batch orchestration</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Row 3 marked as Failed with error reason; batch continues and completes remaining rows</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>UT_19_Analytics_Date_Range_Aggregation</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Query GET /api/analytics with start_date and end_date query parameters</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>History record filtering and KPI aggregation within specific date window</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>HTTP 200 returned with counts, averages, and chart buckets strictly within range</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>UT_20_Executive_PDF_Report_Generation</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Send GET /api/reports/{id}/pdf for completed evaluation record</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>ReportLab PDF canvas creation with styles, tables, and verdict badge</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>HTTP 200 returned with Content-Type application/pdf and valid binary PDF stream</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Passed (generated valid multi-page PDF)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>UT_21_Inspect_Modal_Safe_JSON_Rendering</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Trigger Inspect modal in React on record with null scores and unparsed JSON string details</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Defensive parsing with safeList, safeScore, and InspectErrorBoundary</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Modal renders without throwing TypeError and falls back to safe defaults without screen crash</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>UT_22_Multi_Key_Rotation_Latency</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Execute 4 parallel agent threads concurrently using get_ordered_api_keys()</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Dual GEMINI_API_KEY and GEMINI_API_KEY_2 pool rotation with gemini-3.1-flash-lite</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Zero 429 quota exhaustion errors and total pipeline execution time &lt; 8.0 seconds</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Passed (5.18s total execution time)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>

--- a/agile_methodologyFiles/Unit_Test_Plan_v0.1.xlsx
+++ b/agile_methodologyFiles/Unit_Test_Plan_v0.1.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="UT" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UT" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -464,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F23"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="12.75"/>
   <cols>
     <col width="9.140625" customWidth="1" min="1" max="1"/>
@@ -1166,6 +1166,156 @@
         </is>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>UT_23_Radar_Chart_Coordinate_Bounds</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Compute vertex positions and render SVG polygon on Multi-Agent Quality Radar in Analytics dashboard</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Radar dimensions and label anchor coordinates within 390x270 viewport</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>All 4 dimension text nodes render strictly within SVG bounds without negative X or out-of-boundary clipping</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>UT_24_Inspect_Modal_Claim_Card_Formatting</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Open Inspect modal for batch record containing multi-attribute claim objects</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Defensive parsing of statement, verdict, source, and explanation attributes</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Renders structured modal claim cards with status badges and explanations; zero raw JSON string dumps</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>UT_25_Multi_Provider_Failover</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Simulate primary Gemini quota exhaustion and trigger evaluate_response()</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Automatic failover to secondary OpenAI GPT-4o-mini provider</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Pipeline completes successfully without 429 exception; returns valid 4-dimension evaluation object</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Passed (1.42s failover response)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>UT_26_Batch_PDF_MultiPage_Audit_Table</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Generate batch evaluation PDF report for 10-record CSV dataset via GET /api/reports/batch/{id}/pdf</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Multi-page PDF table compilation with header repetition and page numbering</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Returns valid binary PDF stream; pages contain executive summary and granular record breakdown table</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Passed (generated valid 3-page PDF)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>UT_27_SentryAI_Brand_Integrity</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Inspect document title, favicon link, sidebar title, navbar header, and PDF report metadata</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Unified product brand consistency across all application touchpoints</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>SentryAI title, custom SVG shield icon, and response validation subtitle displayed consistently</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>

--- a/agile_methodologyFiles/Unit_Test_Plan_v0.1.xlsx
+++ b/agile_methodologyFiles/Unit_Test_Plan_v0.1.xlsx
@@ -464,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:F33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="12.75"/>
   <cols>
     <col width="9.140625" customWidth="1" min="1" max="1"/>
@@ -1316,6 +1316,156 @@
         </is>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>UT_28_Analytics_Verdict_Filter_Query</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Send GET /api/analytics with verdict=pass, verdict=fail, and verdict=needs</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Parameterized SQL query execution in get_analytics_summary</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>HTTP 200 returned with exact filtered record counts; zero psycopg2 format exceptions</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>UT_29_Analytics_Engine_Filter_Query</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Send GET /api/analytics with engine=openai and engine=gemini</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Model-specific filtering based on ai_engine database column</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>HTTP 200 returned with distinct record sets and pass rates for each model engine</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>UT_30_Batch_Module_Sample_CSV_Removal</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Inspect Batch Evaluation Module header in web UI</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Verify removal of Download Sample CSV button from interface</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Header displays title and subtitle cleanly without sample CSV download button</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>UT_31_Executive_PDF_NumberedCanvas_Output</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Generate single evaluation PDF and batch PDF via export endpoints</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NumberedCanvas two-pass page numbering and running header</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Returns valid binary PDF stream; pages contain running header and Page X of Y footers</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Passed (generated valid multi-page PDF)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>UT_32_Cloud_Deployment_Health_Check</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Send HEAD and GET requests to /api/health and / on deployed web service</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>FastAPI application gateway health check and database ping</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>HTTP 200 OK returned with status: healthy and database: connected</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Passed (HTTP 200 OK)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>

--- a/agile_methodologyFiles/Unit_Test_Plan_v0.1.xlsx
+++ b/agile_methodologyFiles/Unit_Test_Plan_v0.1.xlsx
@@ -464,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F33"/>
+  <dimension ref="A1:F34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="12.75"/>
   <cols>
     <col width="9.140625" customWidth="1" min="1" max="1"/>
@@ -1466,6 +1466,36 @@
         </is>
       </c>
     </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>UT_33_MIT_License_And_OSS_Governance</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Verify LICENSE file existence, MIT license text format, copyright holder (Nitin Patel 2026), and repository README citation</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Presence of root LICENSE file and valid MIT declaration with open-source reuse permissions</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Standard MIT license file present at repository root; verified copyright declaration and permissiveness clause</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Passed (MIT License verified at repository root)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
